--- a/out/Attention-Mamba1_repeat_3_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.828705708809411</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000129322240074398</v>
+        <v>-0.0003579553554826416</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1664477966935328</v>
+        <v>0.4607164258863827</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3332105926844491</v>
+        <v>0.9223047488680123</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.03843963779865324</v>
+        <v>-0.1063983596705112</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.828705708809411</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1278788366548051</v>
+        <v>0.353960110860389</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1278788366548051</v>
+        <v>0.353960110860389</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1277417688705619</v>
+        <v>0.3534998420322563</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.4211017144827813</v>
+        <v>1.414045382050519</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.970784034957395</v>
+        <v>3.184406300990855</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.080573130334753</v>
+        <v>0.2705615887850193</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7102137405909996</v>
+        <v>2.309420698374884</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1411312616463989</v>
+        <v>0.4739144998377889</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9119430653573821</v>
+        <v>2.986820612342991</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.07728885299023766</v>
+        <v>0.2595325878801432</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9252674276229804</v>
+        <v>3.031563279562619</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03192122505340367</v>
+        <v>0.1071909352535</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.911740395926804</v>
+        <v>2.98614001411229</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.03977110712157154</v>
+        <v>0.1335502163994786</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9593673310508807</v>
+        <v>3.146068484832547</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02394734381520473</v>
+        <v>0.08041507186244143</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.96746412356498</v>
+        <v>3.173256803585467</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01820641902214179</v>
+        <v>0.06113707245868664</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9799200005760037</v>
+        <v>3.215081514296451</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.008051121480334354</v>
+        <v>0.02704108625280412</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.977800388596155</v>
+        <v>3.207972692580757</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.006386284734785004</v>
+        <v>0.02145730557361526</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9825220400176612</v>
+        <v>3.223836478745739</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003164375493607495</v>
+        <v>0.01063879852036297</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9824604537746741</v>
+        <v>3.223641513358855</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001839433272729129</v>
+        <v>0.006182869985954033</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9829707680351731</v>
+        <v>3.225365744017267</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0009172166363645644</v>
+        <v>0.003090389593349832</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9829646198132064</v>
+        <v>3.225356890048268</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000449194409656309</v>
+        <v>0.001524312822387066</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9829480877438556</v>
+        <v>3.225313177030322</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002586745694543162</v>
+        <v>0.000882815638922128</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9830164671091352</v>
+        <v>3.225553691004601</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.427880455887632e-05</v>
+        <v>0.0002918520251582637</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9829227938830303</v>
+        <v>3.225253852527803</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.991582294542086e-05</v>
+        <v>0.0001432222157198888</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9829182908865021</v>
+        <v>3.225250506476898</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.946196130108506e-05</v>
+        <v>7.57244722935807e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9829172731428745</v>
+        <v>3.225258848568685</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>6.850902234816308e-06</v>
+        <v>3.529306759837545e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9829114972000099</v>
+        <v>3.225251210362945</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>8.184014912590811e-07</v>
+        <v>1.827360596503633e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9829091882952079</v>
+        <v>3.225255355740038</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>5.309983785801169e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9829031887616112</v>
+        <v>3.225247353915619</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9828989461514572</v>
+        <v>3.22524424923037</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2554444171274072</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.982899174472492</v>
+        <v>3.22523993023922</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9828992644171419</v>
+        <v>3.225235106066331</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.9828984064835571</v>
+        <v>3.225234248132747</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9828986348045917</v>
+        <v>3.225234476453781</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.98289783914038</v>
+        <v>3.225233680789569</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9828979014097531</v>
+        <v>3.225233743058942</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.98289792908503</v>
+        <v>3.225233770734219</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9828980812990533</v>
+        <v>3.225233922948242</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9828977353580916</v>
+        <v>3.225233577007281</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9828978114651031</v>
+        <v>3.225233653114292</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9828979775167648</v>
+        <v>3.225233819165954</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9828983372953648</v>
+        <v>3.225234178944554</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9828983580518226</v>
+        <v>3.225234199701011</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.982898461834111</v>
+        <v>3.2252343034833</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9828986901551457</v>
+        <v>3.225234531804334</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9828985656163995</v>
+        <v>3.225234407265589</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.9828985932916764</v>
+        <v>3.225234434940865</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9828986486422303</v>
+        <v>3.225234490291419</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.982898911557361</v>
+        <v>3.22523475320655</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9828988285315302</v>
+        <v>3.225234670180719</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9828986209669535</v>
+        <v>3.225234462616143</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9828986348045917</v>
+        <v>3.225234476453781</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9828987731809765</v>
+        <v>3.225234614830165</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9828984895093879</v>
+        <v>3.225234331158577</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9828983165389071</v>
+        <v>3.225234158188096</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9828982127566186</v>
+        <v>3.225234054405807</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9828983580518226</v>
+        <v>3.225234199701011</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9828986002104958</v>
+        <v>3.225234441859685</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9828984272400147</v>
+        <v>3.225234268889204</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9828981297307878</v>
+        <v>3.225233971379977</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9828981158931492</v>
+        <v>3.225233957542339</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.98289774919573</v>
+        <v>3.225233590844919</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.98289774919573</v>
+        <v>3.225233590844919</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9828976869263569</v>
+        <v>3.225233528575546</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9828975831440685</v>
+        <v>3.225233424793257</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9828974101735878</v>
+        <v>3.225233251822777</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9828974586053223</v>
+        <v>3.225233300254512</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9828970988267223</v>
+        <v>3.225232940475911</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9828970573138068</v>
+        <v>3.225232898962996</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9828971126643605</v>
+        <v>3.22523295431355</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-3.228705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9828971680149144</v>
+        <v>3.225233009664104</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9828972095278299</v>
+        <v>3.225233051177019</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9828969396938798</v>
+        <v>3.225232781343069</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9828969950444337</v>
+        <v>3.225232836693623</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9828971403396376</v>
+        <v>3.225232981988827</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9828971057455413</v>
+        <v>3.22523294739473</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9828970919079029</v>
+        <v>3.225232933557092</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.982897181852553</v>
+        <v>3.225233023501742</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9828975001182377</v>
+        <v>3.225233341767427</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-3.228705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9828973202289375</v>
+        <v>3.225233161878127</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9828973617418529</v>
+        <v>3.225233203391042</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9828971749337336</v>
+        <v>3.225233016582923</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9828972441219261</v>
+        <v>3.225233085771115</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9828970434761684</v>
+        <v>3.225232885125358</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9828970849890837</v>
+        <v>3.225232926638272</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9828971126643605</v>
+        <v>3.22523295431355</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.05940387143383</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410505</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000129322240074398</v>
+        <v>-0.0001391288239565911</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1664477966935328</v>
+        <v>0.1790696340460423</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3332105926844491</v>
+        <v>0.3584781539771957</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.03843963779865324</v>
+        <v>-0.04135453884163492</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1278788366548051</v>
+        <v>0.1375759663804509</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1278788366548051</v>
+        <v>0.1375759663804509</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1277417688705619</v>
+        <v>0.1374295300619085</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.4211017144827813</v>
+        <v>0.4498840402453849</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.970784034957395</v>
+        <v>1.038093434827272</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.080573130334753</v>
+        <v>0.0860802419634077</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7102137405909996</v>
+        <v>0.7597133607958031</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1411312616463989</v>
+        <v>0.1507777074845972</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9119430653573821</v>
+        <v>0.9752307296742273</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.07728885299023766</v>
+        <v>0.08257112124717098</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9252674276229804</v>
+        <v>0.9894657803716227</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03192122505340367</v>
+        <v>0.03410307558204893</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.911740395926804</v>
+        <v>0.9750141669885602</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.03977110712157154</v>
+        <v>0.04248999606655025</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9593673310508807</v>
+        <v>1.025896414031542</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02394734381520473</v>
+        <v>0.02558446616540073</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.96746412356498</v>
+        <v>1.034546516619501</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01820641902214179</v>
+        <v>0.01945107211303103</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9799200005760037</v>
+        <v>1.047853262124788</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.008051121480334354</v>
+        <v>0.008601016535018845</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.977800388596155</v>
+        <v>1.045589310877819</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.006386284734785004</v>
+        <v>0.006822627378477903</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9825220400176612</v>
+        <v>1.05063359414893</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003164375493607495</v>
+        <v>0.003382004276515034</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9824604537746741</v>
+        <v>1.050568144528755</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001839433272729129</v>
+        <v>0.001964528904791199</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9829707680351731</v>
+        <v>1.051113409125535</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0009172166363645644</v>
+        <v>0.0009783098520227849</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9829646198132064</v>
+        <v>1.05110718483839</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000449194409656309</v>
+        <v>0.0004808155394425077</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9829480877438556</v>
+        <v>1.051089852311901</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002586745694543162</v>
+        <v>0.0002787004861217326</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9830164671091352</v>
+        <v>1.051163306025486</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.427880455887632e-05</v>
+        <v>8.874274478682012e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9829227938830303</v>
+        <v>1.051064092126999</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.991582294542086e-05</v>
+        <v>4.21616140926919e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9829182908865021</v>
+        <v>1.051059627818283</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.946196130108506e-05</v>
+        <v>2.190815743119357e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9829172731428745</v>
+        <v>1.051059008300293</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9829114972000099</v>
+        <v>1.051053156250417</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>8.184014912590811e-07</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9829091882952079</v>
+        <v>1.051051383391363</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9829031887616112</v>
+        <v>1.051045383857767</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9828989461514572</v>
+        <v>1.051041141247613</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.982899174472492</v>
+        <v>1.051041369568647</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9828992644171419</v>
+        <v>1.051041459513297</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.9828984064835571</v>
+        <v>1.051040601579712</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9828986348045917</v>
+        <v>1.051040829900747</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.98289783914038</v>
+        <v>1.051040034236535</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9828979014097531</v>
+        <v>1.051040096505909</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.98289792908503</v>
+        <v>1.051040124181185</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9828980812990533</v>
+        <v>1.051040276395209</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9828977353580916</v>
+        <v>1.051039930454247</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9828978114651031</v>
+        <v>1.051040006561259</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9828979775167648</v>
+        <v>1.05104017261292</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9828983372953648</v>
+        <v>1.05104053239152</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9828983580518226</v>
+        <v>1.051040553147978</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.982898461834111</v>
+        <v>1.051040656930266</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9828986901551457</v>
+        <v>1.051040885251301</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9828985656163995</v>
+        <v>1.051040760712555</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.9828985932916764</v>
+        <v>1.051040788387832</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9828986486422303</v>
+        <v>1.051040843738386</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.982898911557361</v>
+        <v>1.051041106653516</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9828988285315302</v>
+        <v>1.051041023627686</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9828986209669535</v>
+        <v>1.051040816063109</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9828986348045917</v>
+        <v>1.051040829900747</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9828987731809765</v>
+        <v>1.051040968277132</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9828984895093879</v>
+        <v>1.051040684605543</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9828983165389071</v>
+        <v>1.051040511635063</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9828982127566186</v>
+        <v>1.051040407852774</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9828983580518226</v>
+        <v>1.051040553147978</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9828986002104958</v>
+        <v>1.051040795306651</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9828984272400147</v>
+        <v>1.05104062233617</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9828981297307878</v>
+        <v>1.051040324826943</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9828981158931492</v>
+        <v>1.051040310989305</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.98289774919573</v>
+        <v>1.051039944291885</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2554444171274072</v>
+        <v>0.3408761717445079</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.98289774919573</v>
+        <v>1.051039944291885</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.3926438570410506</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9828976869263569</v>
+        <v>1.051039882022512</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.3926438570410506</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9828975831440685</v>
+        <v>1.051039778240224</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9828974101735878</v>
+        <v>1.051039605269743</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9828974586053223</v>
+        <v>1.051039653701478</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9828970988267223</v>
+        <v>1.051039293922878</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2554444171274072</v>
+        <v>-0.5926438570410505</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9828970573138068</v>
+        <v>1.051039252409962</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.5926438570410505</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9828971126643605</v>
+        <v>1.051039307760516</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-3.228705708809411</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9828971680149144</v>
+        <v>1.05103936311107</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-3.828705708809411</v>
+        <v>-2.459683914612167</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9828972095278299</v>
+        <v>1.051039404623985</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9828969396938798</v>
+        <v>1.051039134790035</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9828969950444337</v>
+        <v>1.051039190140589</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.3926438570410506</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9828971403396376</v>
+        <v>1.051039335435793</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8554444171274072</v>
+        <v>-1.326163885826609</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9828971057455413</v>
+        <v>1.051039300841697</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.3926438570410506</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9828970919079029</v>
+        <v>1.051039287004058</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.3926438570410506</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.982897181852553</v>
+        <v>1.051039376948709</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.3926438570410506</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9828975001182377</v>
+        <v>1.051039695214393</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-3.228705708809411</v>
+        <v>-1.326163885826609</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9828973202289375</v>
+        <v>1.051039515325093</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-3.828705708809411</v>
+        <v>-1.326163885826609</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9828973617418529</v>
+        <v>1.051039556838008</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2554444171274072</v>
+        <v>-1.526163885826609</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9828971749337336</v>
+        <v>1.051039370029889</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-3.828705708809411</v>
+        <v>-0.5926438570410507</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9828972441219261</v>
+        <v>1.051039439218082</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8554444171274072</v>
+        <v>-0.3926438570410508</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9828970434761684</v>
+        <v>1.051039238572324</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9828970849890837</v>
+        <v>1.051039280085239</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8554444171274072</v>
+        <v>0.5408761717445079</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9828971126643605</v>
+        <v>1.051039307760516</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-6.188079714775085e-05</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.05940387143383</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.001216281205415726</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5926438570410505</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.001400016248226166</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.001674454659223557</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0001933574676513672</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.00141177698969841</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0007155910134315491</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.001535661518573761</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001210156828165054</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0001559779047966003</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001055192202329636</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001222770661115646</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001925788819789886</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0007839538156986237</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0009499788284301758</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001108158379793167</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001794241368770599</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001757200807332993</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001989834010601044</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0007017776370048523</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.000416100025177002</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001026853919029236</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001317095011472702</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002173800021409988</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007546022534370422</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.003647420555353165</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.00451008602976799</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0003447122871875763</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>5.652382969856262e-05</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001077622175216675</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0001617446541786194</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0003890953958034515</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001276932656764984</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002760756760835648</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0002697072923183441</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0005868375301361084</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001526970416307449</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>4.706531763076782e-05</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0008000209927558899</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001375153660774231</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003341350704431534</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.005121868103742599</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0105726420879364</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001391288239565911</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1790696340460423</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.004944663494825363</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5926438570410507</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3584781539771957</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04135453884163492</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.002458278089761734</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5926438570410507</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1375759663804509</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.004115670919418335</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5926438570410507</v>
+        <v>0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1375759663804509</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.003849491477012634</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1374295300619085</v>
+        <v>0.1805213941220674</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.4498840402453849</v>
+        <v>0.271009254272278</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>7.790327072143555e-05</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.038093434827272</v>
+        <v>0.7230795454343113</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0860802419634077</v>
+        <v>0.05185450506984655</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.006536688655614853</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7597133607958031</v>
+        <v>0.5553839406986648</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1507777074845972</v>
+        <v>0.09082808341202726</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.003623340278863907</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9752307296742273</v>
+        <v>0.6852113324793528</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.08257112124717098</v>
+        <v>0.0497410020264745</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.003545772284269333</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9894657803716227</v>
+        <v>0.6937865293520289</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03410307558204893</v>
+        <v>0.02054356141809943</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.003482021391391754</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9750141669885602</v>
+        <v>0.6850809000840403</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04248999606655025</v>
+        <v>0.02559600501737523</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.015577532351017</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.025896414031542</v>
+        <v>0.7157324032888799</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02558446616540073</v>
+        <v>0.01541210131699671</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.004330433905124664</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.034546516619501</v>
+        <v>0.7209432314776005</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01945107211303103</v>
+        <v>0.01171606775438062</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.02644619159400463</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5926438570410507</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.047853262124788</v>
+        <v>0.7289579523447307</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.008601016535018845</v>
+        <v>0.005179270717863615</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002414986491203308</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5926438570410507</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.045589310877819</v>
+        <v>0.7275921584448952</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.006822627378477903</v>
+        <v>0.004108727467416868</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.005817331373691559</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5926438570410507</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.05063359414893</v>
+        <v>0.7306288494663095</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003382004276515034</v>
+        <v>0.002033706414593613</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.06595078110694885</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.050568144528755</v>
+        <v>0.7305874428601901</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001964528904791199</v>
+        <v>0.001181953904216853</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.0492798313498497</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3408761717445079</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.051113409125535</v>
+        <v>0.7309140646555904</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0009783098520227849</v>
+        <v>0.0005884769521084263</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01332541927695274</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.05110718483839</v>
+        <v>0.7309083257367219</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0004808155394425077</v>
+        <v>0.0002882141125629336</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.02138148993253708</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.051089852311901</v>
+        <v>0.7308959033159879</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002787004861217326</v>
+        <v>0.0001652202916730396</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.02657047659158707</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.051163306025486</v>
+        <v>0.7309379755441389</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.874274478682012e-05</v>
+        <v>5.079925284929769e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.003547057509422302</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.051064092126999</v>
+        <v>0.7308764477667462</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.21616140926919e-05</v>
+        <v>2.419528491452356e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.008788570761680603</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.051059627818283</v>
+        <v>0.7308717708190028</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.190815743119357e-05</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.004304274916648865</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.051059008300293</v>
+        <v>0.730869360818584</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>6.850902234816308e-06</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01094270125031471</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.051053156250417</v>
+        <v>0.7308638191458536</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01220978051424026</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.051051383391363</v>
+        <v>0.7308609705731517</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.009064484387636185</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.051045383857767</v>
+        <v>0.7308553031428779</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01630488038063049</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.051041141247613</v>
+        <v>0.7308556836779357</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.004520416259765625</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.051041369568647</v>
+        <v>0.7308559119989705</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.005367789417505264</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.051041459513297</v>
+        <v>0.7308560019436204</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.004152841866016388</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.051040601579712</v>
+        <v>0.7308551440100356</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.006092824041843414</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.051040829900747</v>
+        <v>0.7308553723310702</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.005045857280492783</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.051040034236535</v>
+        <v>0.7308545766668585</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0002543404698371887</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.051040096505909</v>
+        <v>0.7308546389362316</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.0033847875893116</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.051040124181185</v>
+        <v>0.7308546666115084</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.004988372325897217</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.051040276395209</v>
+        <v>0.7308548188255317</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0002749338746070862</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.051039930454247</v>
+        <v>0.7308544728845701</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.002993699163198471</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.051040006561259</v>
+        <v>0.7308545489915816</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0004773736000061035</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.05104017261292</v>
+        <v>0.7308547150432433</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.007784437388181686</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.05104053239152</v>
+        <v>0.7308550748218433</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.007882464677095413</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.051040553147978</v>
+        <v>0.730855095578301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01115616410970688</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.051040656930266</v>
+        <v>0.7308551993605895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.002551965415477753</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.051040885251301</v>
+        <v>0.7308554276816241</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.002175871282815933</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5408761717445079</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.051040760712555</v>
+        <v>0.7308553031428779</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.002350110560655594</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.051040788387832</v>
+        <v>0.7308553308181549</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.009258892387151718</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.051040843738386</v>
+        <v>0.7308553861687088</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.001272641122341156</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.051041106653516</v>
+        <v>0.7308556490838395</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.003068942576646805</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.051041023627686</v>
+        <v>0.7308555660580087</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.002878166735172272</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.051040816063109</v>
+        <v>0.730855358493432</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.002874255180358887</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.051040829900747</v>
+        <v>0.7308553723310702</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.001800395548343658</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.051040968277132</v>
+        <v>0.730855510707455</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0003130324184894562</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.051040684605543</v>
+        <v>0.7308552270358664</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0008084326982498169</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.051040511635063</v>
+        <v>0.7308550540653856</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.00485658273100853</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.051040407852774</v>
+        <v>0.7308549502830971</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.002527616918087006</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.051040553147978</v>
+        <v>0.730855095578301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.001486651599407196</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.051040795306651</v>
+        <v>0.7308553377369742</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0002158321440219879</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.05104062233617</v>
+        <v>0.7308551647664933</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0005896613001823425</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.051040324826943</v>
+        <v>0.7308548672572663</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.0002280920743942261</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.051040310989305</v>
+        <v>0.7308548534196277</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0001924224197864532</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.051039944291885</v>
+        <v>0.7308544867222085</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.002553585916757584</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3408761717445079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.051039944291885</v>
+        <v>0.7308544867222085</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.001054096966981888</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3926438570410506</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.051039882022512</v>
+        <v>0.7308544244528354</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.001373667269945145</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3926438570410506</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.051039778240224</v>
+        <v>0.730854320670547</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.000500313937664032</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.051039605269743</v>
+        <v>0.7308541477000662</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.0006581172347068787</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.051039653701478</v>
+        <v>0.7308541961318008</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.001096338033676147</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.051039293922878</v>
+        <v>0.7308538363532007</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0003991946578025818</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5926438570410505</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.051039252409962</v>
+        <v>0.7308537948402853</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0009926892817020416</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5926438570410505</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.051039307760516</v>
+        <v>0.730853850190839</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0006698332726955414</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.05103936311107</v>
+        <v>0.730853905541393</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.0006608106195926666</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.459683914612167</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.051039404623985</v>
+        <v>0.7308539470543084</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.0005358494818210602</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.051039134790035</v>
+        <v>0.7308536772203583</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0008747875690460205</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.051039190140589</v>
+        <v>0.7308537325709122</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.0002139806747436523</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3926438570410506</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.051039335435793</v>
+        <v>0.7308538778661161</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0002728663384914398</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.326163885826609</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.051039300841697</v>
+        <v>0.7308538432720199</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.0001321099698543549</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3926438570410506</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.051039287004058</v>
+        <v>0.7308538294343814</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.004284922033548355</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3926438570410506</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.051039376948709</v>
+        <v>0.7308539193790315</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.007663290947675705</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3926438570410506</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.051039695214393</v>
+        <v>0.7308542376447161</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002266734838485718</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.326163885826609</v>
+        <v>0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.051039515325093</v>
+        <v>0.730854057755416</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0002147965133190155</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.326163885826609</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.051039556838008</v>
+        <v>0.7308540992683314</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.000874057412147522</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.526163885826609</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.051039370029889</v>
+        <v>0.7308539124602121</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001002795994281769</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5926438570410507</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.051039439218082</v>
+        <v>0.7308539816484046</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0002666525542736053</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3926438570410508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.051039238572324</v>
+        <v>0.7308537810026468</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>6.974115967750549e-05</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.7199999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.051039280085239</v>
+        <v>0.7308538225155622</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.000402156263589859</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5408761717445079</v>
+        <v>-0.7199999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.051039307760516</v>
+        <v>0.730853850190839</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000006.xlsx
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.001216281205415726</v>
+        <v>0.001216288655996323</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.001674454659223557</v>
+        <v>0.001674450933933258</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.0001933574676513672</v>
+        <v>0.0001933351159095764</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.00141177698969841</v>
+        <v>0.001411791890859604</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.0007155910134315491</v>
+        <v>0.0007155835628509521</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.001535661518573761</v>
+        <v>0.00153568759560585</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.001210156828165054</v>
+        <v>0.001210164278745651</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0001559779047966003</v>
+        <v>0.0001559853553771973</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.001055192202329636</v>
+        <v>0.001055169850587845</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.001222770661115646</v>
+        <v>0.001222740858793259</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0007839538156986237</v>
+        <v>0.0007839761674404144</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0009499788284301758</v>
+        <v>0.000950004905462265</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.001108158379793167</v>
+        <v>0.00110815092921257</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.001794241368770599</v>
+        <v>0.001794237643480301</v>
       </c>
       <c r="JB18" t="n">
         <v>0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.001757200807332993</v>
+        <v>0.001757204532623291</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.001989834010601044</v>
+        <v>0.001989841461181641</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0007017776370048523</v>
+        <v>0.0007017999887466431</v>
       </c>
       <c r="JB21" t="n">
         <v>0.16</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.000416100025177002</v>
+        <v>0.0004161074757575989</v>
       </c>
       <c r="JB22" t="n">
         <v>0.16</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.001026853919029236</v>
+        <v>0.001026883721351624</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.001317095011472702</v>
+        <v>0.001317113637924194</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.002173800021409988</v>
+        <v>0.00217379629611969</v>
       </c>
       <c r="JB25" t="n">
         <v>0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0007546022534370422</v>
+        <v>0.0007546059787273407</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.003647420555353165</v>
+        <v>0.003647428005933762</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.00451008602976799</v>
+        <v>0.004510093480348587</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0003447122871875763</v>
+        <v>0.0003447309136390686</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>5.652382969856262e-05</v>
+        <v>5.65163791179657e-05</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.001077622175216675</v>
+        <v>0.001077599823474884</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0001617446541786194</v>
+        <v>0.0001617632806301117</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0003890953958034515</v>
+        <v>0.00038909912109375</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.001276932656764984</v>
+        <v>0.001276936382055283</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.002760756760835648</v>
+        <v>0.002760745584964752</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.0002697072923183441</v>
+        <v>0.0002696923911571503</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0005868375301361084</v>
+        <v>0.0005868449807167053</v>
       </c>
       <c r="JB37" t="n">
         <v>0.02000000000000007</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001526970416307449</v>
+        <v>0.001526981592178345</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>4.706531763076782e-05</v>
+        <v>4.702433943748474e-05</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.0008000209927558899</v>
+        <v>0.0008000247180461884</v>
       </c>
       <c r="JB40" t="n">
         <v>0.3</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.003341350704431534</v>
+        <v>0.003341320902109146</v>
       </c>
       <c r="JB42" t="n">
         <v>0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.005121868103742599</v>
+        <v>0.005121845752000809</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.004944663494825363</v>
+        <v>0.004944700747728348</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.002458278089761734</v>
+        <v>-0.002458270639181137</v>
       </c>
       <c r="JB46" t="n">
         <v>0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.004115670919418335</v>
+        <v>0.00411565974354744</v>
       </c>
       <c r="JB47" t="n">
         <v>0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.003849491477012634</v>
+        <v>0.003849498927593231</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>7.790327072143555e-05</v>
+        <v>7.791444659233093e-05</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.02000000000000007</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.006536688655614853</v>
+        <v>0.006536681205034256</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.16</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.003623340278863907</v>
+        <v>0.003623351454734802</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.16</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.003545772284269333</v>
+        <v>0.003545742481946945</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.015577532351017</v>
+        <v>0.01557750627398491</v>
       </c>
       <c r="JB54" t="n">
         <v>0.5799999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.004330433905124664</v>
+        <v>0.004330426454544067</v>
       </c>
       <c r="JB55" t="n">
         <v>0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.02644619159400463</v>
+        <v>0.02644620835781097</v>
       </c>
       <c r="JB56" t="n">
         <v>0.5799999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.002414986491203308</v>
+        <v>-0.00241498276591301</v>
       </c>
       <c r="JB57" t="n">
         <v>0.5799999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.005817331373691559</v>
+        <v>0.005817323923110962</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.06595078110694885</v>
+        <v>0.06595079600811005</v>
       </c>
       <c r="JB59" t="n">
         <v>0.5799999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.0492798313498497</v>
+        <v>0.04927982017397881</v>
       </c>
       <c r="JB60" t="n">
         <v>0.8599999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.01332541927695274</v>
+        <v>0.01332540810108185</v>
       </c>
       <c r="JB61" t="n">
         <v>0.8599999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.02138148993253708</v>
+        <v>0.0213814489543438</v>
       </c>
       <c r="JB62" t="n">
         <v>0.5799999999999998</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.02657047659158707</v>
+        <v>0.02657043375074863</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
         <v>0.7309379755441389</v>
@@ -51824,7 +51824,7 @@
         <v>0.003547057509422302</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0.7308764477667462</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.008788570761680603</v>
+        <v>0.008788533508777618</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0.7308717708190028</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.004304274916648865</v>
+        <v>0.004304263740777969</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0.730869360818584</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.01094270125031471</v>
+        <v>0.01094271242618561</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0.7308638191458536</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.01220978051424026</v>
+        <v>0.01220977678894997</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0.7308609705731517</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.009064484387636185</v>
+        <v>0.009064465761184692</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0.7308553031428779</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.01630488038063049</v>
+        <v>0.01630483940243721</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0.7308556836779357</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.004520416259765625</v>
+        <v>0.004520401358604431</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0.7308559119989705</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.005367789417505264</v>
+        <v>0.005367770791053772</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.006092824041843414</v>
+        <v>0.006092827767133713</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.005045857280492783</v>
+        <v>0.005045868456363678</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.0033847875893116</v>
+        <v>0.003384806215763092</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.004988372325897217</v>
+        <v>0.004988376051187515</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.0002749338746070862</v>
+        <v>-0.0002749077975749969</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.002993699163198471</v>
+        <v>0.002993673086166382</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.0004773736000061035</v>
+        <v>0.0004773624241352081</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66134,7 +66134,7 @@
         <v>0.007784437388181686</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0.7308550748218433</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.007882464677095413</v>
+        <v>0.00788247212767601</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0.730855095578301</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.01115616410970688</v>
+        <v>0.01115620508790016</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0.7308551993605895</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.002551965415477753</v>
+        <v>0.002551957964897156</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0.7308554276816241</v>
@@ -69314,7 +69314,7 @@
         <v>0.002175871282815933</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0.7308553031428779</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.002350110560655594</v>
+        <v>0.002350103110074997</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0.7308553308181549</v>
@@ -70904,7 +70904,7 @@
         <v>0.009258892387151718</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0.7308553861687088</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.001272641122341156</v>
+        <v>0.001272622495889664</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0.7308556490838395</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.003068942576646805</v>
+        <v>0.003068964928388596</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0.7308555660580087</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.002878166735172272</v>
+        <v>0.002878174185752869</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.002874255180358887</v>
+        <v>0.002874240279197693</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.001800395548343658</v>
+        <v>0.001800380647182465</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.0003130324184894562</v>
+        <v>0.0003130659461021423</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0.7308552270358664</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.0008084326982498169</v>
+        <v>0.000808417797088623</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0.7308550540653856</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.00485658273100853</v>
+        <v>0.004856571555137634</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.2599999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.002527616918087006</v>
+        <v>0.002527587115764618</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.2599999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.001486651599407196</v>
+        <v>0.001486670225858688</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.2599999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.0002158321440219879</v>
+        <v>-0.0002158172428607941</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.3999999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0005896613001823425</v>
+        <v>0.0005896538496017456</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.0002280920743942261</v>
+        <v>-0.0002280957996845245</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.0001924224197864532</v>
+        <v>0.0001924596726894379</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.002553585916757584</v>
+        <v>0.002553589642047882</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.001054096966981888</v>
+        <v>0.001054104417562485</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.001373667269945145</v>
+        <v>-0.001373626291751862</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.000500313937664032</v>
+        <v>0.0005003027617931366</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.0006581172347068787</v>
+        <v>-0.0006581470370292664</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.001096338033676147</v>
+        <v>-0.001096315681934357</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0009926892817020416</v>
+        <v>0.0009926781058311462</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.0006698332726955414</v>
+        <v>-0.0006698369979858398</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.0006608106195926666</v>
+        <v>-0.0006607994437217712</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.0005358494818210602</v>
+        <v>-0.0005358569324016571</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0008747875690460205</v>
+        <v>0.0008747950196266174</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.0002139806747436523</v>
+        <v>-0.0002139844000339508</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.0002728663384914398</v>
+        <v>0.0002728402614593506</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.1199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.0001321099698543549</v>
+        <v>-0.0001321248710155487</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.004284922033548355</v>
+        <v>0.004284914582967758</v>
       </c>
       <c r="JB118" t="n">
         <v>0.1600000000000001</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.007663290947675705</v>
+        <v>0.007663331925868988</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1600000000000001</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002266734838485718</v>
+        <v>-0.002266749739646912</v>
       </c>
       <c r="JB120" t="n">
         <v>0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.0002147965133190155</v>
+        <v>-0.0002147778868675232</v>
       </c>
       <c r="JB121" t="n">
         <v>0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.000874057412147522</v>
+        <v>0.0008740462362766266</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.2599999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.001002795994281769</v>
+        <v>-0.00100281834602356</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0002666525542736053</v>
+        <v>0.0002666302025318146</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>6.974115967750549e-05</v>
+        <v>6.974488496780396e-05</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.7199999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.000402156263589859</v>
+        <v>0.0004021450877189636</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.7199999999999998</v>
